--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.47320202546</v>
+        <v>46073.63986869213</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55105804398</v>
+        <v>46092.717724710645</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.67286997685</v>
+        <v>46134.839536643514</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1487,13 +1487,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.473202361114</v>
+        <v>46073.63986902778</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.551027951384</v>
+        <v>46092.717694618055</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.711198391204</v>
+        <v>46133.877865057875</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1552,13 +1552,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.47320267362</v>
+        <v>46073.63986934027</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55102846065</v>
+        <v>46092.717695127314</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55105918982</v>
+        <v>46092.71772585648</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1617,13 +1617,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.47320296297</v>
+        <v>46073.63986962963</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55102888889</v>
+        <v>46092.717695555555</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.551059062505</v>
+        <v>46092.71772572916</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1682,13 +1682,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.47320327546</v>
+        <v>46073.639869942126</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55102929398</v>
+        <v>46092.717695960644</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6169716088</v>
+        <v>46100.78363827546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1747,13 +1747,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.47320356482</v>
+        <v>46073.63987023148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.551029988426</v>
+        <v>46092.71769665509</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55105956018</v>
+        <v>46092.71772622685</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1812,13 +1812,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.47320385417</v>
+        <v>46073.639870520834</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.4824815162</v>
+        <v>46128.64914818287</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.482493206015</v>
+        <v>46128.649159872686</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1865,13 +1865,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.47320415509</v>
+        <v>46073.63987082176</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.45268501157</v>
+        <v>46099.61935167824</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.4527074537</v>
+        <v>46099.619374120375</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1930,13 +1930,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.4732044213</v>
+        <v>46073.63987108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.48246758102</v>
+        <v>46128.64913424768</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.48248333333</v>
+        <v>46128.64915</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1995,13 +1995,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.47320472222</v>
+        <v>46073.63987138889</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.613279513884</v>
+        <v>46107.779946180555</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.67281400463</v>
+        <v>46134.8394806713</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2044,13 +2044,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.473201747685</v>
+        <v>46073.63986841435</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38388858797</v>
+        <v>46097.55055525463</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38390494213</v>
+        <v>46097.550571608794</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2109,13 +2109,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.4732027662</v>
+        <v>46073.63986943287</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.613189282405</v>
+        <v>46107.77985594908</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.61320850694</v>
+        <v>46107.77987517361</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2174,13 +2174,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.473203333335</v>
+        <v>46073.63987</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38410105324</v>
+        <v>46097.550767719906</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.384115567125</v>
+        <v>46097.5507822338</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2239,13 +2239,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.473203912035</v>
+        <v>46073.6398705787</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.61325946759</v>
+        <v>46107.77992613426</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.61328074074</v>
+        <v>46107.77994740741</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2304,13 +2304,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.47320421296</v>
+        <v>46073.63987087963</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.61339271991</v>
+        <v>46107.780059386576</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.61340555556</v>
+        <v>46107.780072222224</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2357,13 +2357,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.47320450231</v>
+        <v>46073.63987116898</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.61333596065</v>
+        <v>46107.78000262732</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.61335266204</v>
+        <v>46107.780019328704</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2422,13 +2422,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.47320512732</v>
+        <v>46073.63987179398</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3839482176</v>
+        <v>46097.550614884254</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.383963333334</v>
+        <v>46097.55063</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2487,13 +2487,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.473205393515</v>
+        <v>46073.63987206019</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.4531492824</v>
+        <v>46099.619815949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.45316443287</v>
+        <v>46099.61983109954</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2552,13 +2552,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.47320603009</v>
+        <v>46073.63987269676</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.6133721875</v>
+        <v>46107.780038854165</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.67010960648</v>
+        <v>46134.83677627315</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2617,13 +2617,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.47320162037</v>
+        <v>46073.639868287035</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38417290509</v>
+        <v>46097.55083957176</v>
       </c>
       <c r="D23" s="8">
-        <v>46100.61713012731</v>
+        <v>46100.783796793985</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2682,13 +2682,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.473202002315</v>
+        <v>46073.63986866898</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.43624460648</v>
+        <v>46112.60291127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.67292525463</v>
+        <v>46134.83959192129</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2731,13 +2731,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.473202291665</v>
+        <v>46073.63986895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.61349069445</v>
+        <v>46107.78015736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.61361734953</v>
+        <v>46107.780284016204</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2796,13 +2796,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.6134215625</v>
+        <v>46107.78008822916</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.613423194445</v>
+        <v>46107.78008986111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2857,13 +2857,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.4732028588</v>
+        <v>46073.63986952546</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.61347625</v>
+        <v>46107.78014291667</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.61347780093</v>
+        <v>46107.78014446759</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2918,13 +2918,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.473203194444</v>
+        <v>46073.639869861116</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.48235068287</v>
+        <v>46128.64901734954</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.48236672454</v>
+        <v>46128.64903339121</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2983,13 +2983,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.47320350695</v>
+        <v>46073.63987017361</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.45325313657</v>
+        <v>46099.61991980324</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.45325627315</v>
+        <v>46099.61992293982</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3044,13 +3044,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.48233392361</v>
+        <v>46128.649000590274</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.48233547454</v>
+        <v>46128.6490021412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3105,13 +3105,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.47320414352</v>
+        <v>46073.639870810184</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.67630746528</v>
+        <v>46125.84297413194</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.67630875</v>
+        <v>46125.84297541667</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3170,13 +3170,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.61512428241</v>
+        <v>46107.78179094907</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.615125729164</v>
+        <v>46107.781792395836</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3231,13 +3231,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.47320165509</v>
+        <v>46073.639868321756</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.615166759264</v>
+        <v>46107.78183342592</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.61516832176</v>
+        <v>46107.781834988426</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3292,13 +3292,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.47320199074</v>
+        <v>46073.63986865741</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.61433643519</v>
+        <v>46107.78100310185</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.61435130787</v>
+        <v>46107.781017974536</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3357,13 +3357,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.47320226852</v>
+        <v>46073.639868935184</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38403153935</v>
+        <v>46097.55069820602</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38403320602</v>
+        <v>46097.550699872685</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3418,13 +3418,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.614281284725</v>
+        <v>46107.78094795139</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.61428275463</v>
+        <v>46107.7809494213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3479,13 +3479,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.47320282407</v>
+        <v>46073.63986949074</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.61431892361</v>
+        <v>46107.780985590274</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.61432079861</v>
+        <v>46107.780987465274</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3540,13 +3540,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.473203113426</v>
+        <v>46073.63986978009</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38428215278</v>
+        <v>46097.550948819444</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38429922453</v>
+        <v>46097.550965891205</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3605,13 +3605,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.47320342592</v>
+        <v>46073.63987009259</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.38422917824</v>
+        <v>46097.550895844906</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.384230474534</v>
+        <v>46097.550897141205</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3666,13 +3666,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.473203726855</v>
+        <v>46073.63987039352</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.384267256944</v>
+        <v>46097.550933923616</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.38426866898</v>
+        <v>46097.55093533565</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3727,11 +3727,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.47320400463</v>
+        <v>46073.63987067129</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.672963715275</v>
+        <v>46134.839630381946</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3774,13 +3774,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.473204317124</v>
+        <v>46073.639870983796</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.35206908565</v>
+        <v>46114.51873575231</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.35208997685</v>
+        <v>46114.51875664352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3839,13 +3839,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.47320364583</v>
+        <v>46073.6398703125</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.62359909722</v>
+        <v>46114.79026576389</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.62361700232</v>
+        <v>46114.79028366898</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3904,13 +3904,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.513128437495</v>
+        <v>46090.679795104166</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.62364924769</v>
+        <v>46114.79031591435</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.623666053245</v>
+        <v>46114.79033271991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3967,11 +3967,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.513180891205</v>
+        <v>46090.67984755787</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46112.63231680555</v>
+        <v>46112.798983472225</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4028,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.47320399305</v>
+        <v>46073.639870659725</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.537065682875</v>
+        <v>46122.70373234954</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.5370834375</v>
+        <v>46122.70375010416</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4081,13 +4081,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.473204270835</v>
+        <v>46073.6398709375</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.4897806713</v>
+        <v>46122.65644733796</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.489798298615</v>
+        <v>46122.65646496528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4146,13 +4146,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.47320453703</v>
+        <v>46073.639871203704</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.5370488426</v>
+        <v>46122.703715509255</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.537065462966</v>
+        <v>46122.70373212963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4211,11 +4211,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.473204803246</v>
+        <v>46073.6398714699</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46128.32760954861</v>
+        <v>46128.49427621528</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4258,13 +4258,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.473205092596</v>
+        <v>46073.63987175926</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.327605011575</v>
+        <v>46128.49427167824</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.32761921296</v>
+        <v>46128.49428587963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4323,11 +4323,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.473205381946</v>
+        <v>46073.63987204861</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46142.51073898148</v>
+        <v>46142.67740564815</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4386,11 +4386,11 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4732056713</v>
+        <v>46073.63987233797</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46114.62365681713</v>
+        <v>46114.7903234838</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4447,11 +4447,11 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.473205937495</v>
+        <v>46073.639872604166</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46128.482413391204</v>
+        <v>46128.64908005787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4494,11 +4494,11 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.47320619213</v>
+        <v>46073.639872858796</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46127.49450168981</v>
+        <v>46127.661168356484</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4557,13 +4557,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48240732639</v>
+        <v>46128.64907399306</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.482422650464</v>
+        <v>46128.64908931713</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4620,11 +4620,11 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.473202939815</v>
+        <v>46073.639869606486</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46128.50433447916</v>
+        <v>46128.671001145834</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4683,13 +4683,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.47320324074</v>
+        <v>46073.639869907405</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.490245243054</v>
+        <v>46122.656911909726</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.49026456018</v>
+        <v>46122.656931226855</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4746,11 +4746,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.47320353009</v>
+        <v>46073.639870196756</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46090.52693173611</v>
+        <v>46090.69359840278</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4793,11 +4793,11 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46090.67912407407</v>
+        <v>46090.84579074074</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4856,11 +4856,11 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.47320417824</v>
+        <v>46073.63987084491</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46122.49025321759</v>
+        <v>46122.65691988426</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4917,11 +4917,11 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46114.62365734954</v>
+        <v>46114.790324016205</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -4980,11 +4980,11 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4732047338</v>
+        <v>46073.63987140046</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46114.62365793981</v>
+        <v>46114.79032460648</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5043,11 +5043,11 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.47320501157</v>
+        <v>46073.63987167824</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46090.679110150464</v>
+        <v>46090.84577681713</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5104,11 +5104,11 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.473205277776</v>
+        <v>46073.63987194444</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46090.679105034724</v>
+        <v>46090.84577170139</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5165,11 +5165,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.473202106485</v>
+        <v>46073.63986877315</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46090.524304756946</v>
+        <v>46090.69097142361</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5212,11 +5212,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46090.67915795139</v>
+        <v>46090.84582461805</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5273,11 +5273,11 @@
         <v>239</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.473202905094</v>
+        <v>46073.63986957176</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46128.4824731713</v>
+        <v>46128.64913983796</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>240</v>
@@ -5334,11 +5334,11 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.47320325232</v>
+        <v>46073.63986991898</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46090.679239942125</v>
+        <v>46090.845906608796</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5395,11 +5395,11 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.473203587964</v>
+        <v>46073.63987025463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46090.67923677083</v>
+        <v>46090.8459034375</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>247</v>
@@ -5456,11 +5456,11 @@
         <v>249</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.47320392361</v>
+        <v>46073.63987059028</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.47486043982</v>
+        <v>46083.641527106476</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>250</v>
@@ -5503,11 +5503,11 @@
         <v>252</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.47320424768</v>
+        <v>46073.639870914354</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.679287465275</v>
+        <v>46090.845954131946</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>253</v>
@@ -5566,11 +5566,11 @@
         <v>256</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.47320460648</v>
+        <v>46073.639871273146</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.61326695602</v>
+        <v>46107.77993362269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>257</v>
@@ -5629,11 +5629,11 @@
         <v>259</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.51352017361</v>
+        <v>46090.680186840276</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.52080292824</v>
+        <v>46090.68746959491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>260</v>
@@ -5676,11 +5676,11 @@
         <v>262</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.51365603009</v>
+        <v>46090.68032269676</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.679375949076</v>
+        <v>46090.84604261574</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>263</v>
@@ -5739,11 +5739,11 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.51372481481</v>
+        <v>46090.68039148148</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.67937304398</v>
+        <v>46090.84603971065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46128.64908005787</v>
+        <v>46193.564339317134</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,9 +4498,11 @@
       <c r="B54" s="5">
         <v>46073.639872858796</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46193.56431931713</v>
+      </c>
       <c r="D54" s="5">
-        <v>46127.661168356484</v>
+        <v>46193.56432179398</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4624,9 +4626,11 @@
       <c r="B56" s="5">
         <v>46073.639869606486</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46193.56433421296</v>
+      </c>
       <c r="D56" s="5">
-        <v>46128.671001145834</v>
+        <v>46193.564335787036</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4752,7 +4756,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46090.69359840278</v>
+        <v>46193.61410849537</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4797,9 +4801,11 @@
       <c r="B59" s="8">
         <v>46073.639870486106</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46193.61403773148</v>
+      </c>
       <c r="D59" s="8">
-        <v>46090.84579074074</v>
+        <v>46193.614040625005</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4860,9 +4866,11 @@
       <c r="B60" s="5">
         <v>46073.63987084491</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46193.61407924768</v>
+      </c>
       <c r="D60" s="5">
-        <v>46122.65691988426</v>
+        <v>46193.61408086805</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4921,9 +4929,11 @@
       <c r="B61" s="8">
         <v>46073.63987109954</v>
       </c>
-      <c r="C61" s="9"/>
+      <c r="C61" s="8">
+        <v>46193.6140899537</v>
+      </c>
       <c r="D61" s="8">
-        <v>46114.790324016205</v>
+        <v>46193.61409614583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -4984,9 +4994,11 @@
       <c r="B62" s="5">
         <v>46073.63987140046</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46193.61410039352</v>
+      </c>
       <c r="D62" s="5">
-        <v>46114.79032460648</v>
+        <v>46193.61410226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5049,7 +5061,7 @@
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46090.84577681713</v>
+        <v>46193.614372870376</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5110,7 +5122,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46090.84577170139</v>
+        <v>46193.564154085645</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -3971,7 +3971,7 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46112.798983472225</v>
+        <v>46195.56824368055</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46193.61410849537</v>
+        <v>46195.56824184028</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -5059,9 +5059,11 @@
       <c r="B63" s="8">
         <v>46073.63987167824</v>
       </c>
-      <c r="C63" s="9"/>
+      <c r="C63" s="8">
+        <v>46195.56823568287</v>
+      </c>
       <c r="D63" s="8">
-        <v>46193.614372870376</v>
+        <v>46195.56823783564</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5230,7 +5232,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46090.84582461805</v>
+        <v>46195.567961782406</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5352,7 +5354,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46090.845906608796</v>
+        <v>46195.56842914352</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46191.881109062495</v>
+        <v>46195.913107650464</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4390,9 +4390,11 @@
       <c r="B52" s="5">
         <v>46073.63987233797</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46195.91309923611</v>
+      </c>
       <c r="D52" s="5">
-        <v>46191.88111327546</v>
+        <v>46195.9131012963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4805,7 +4807,7 @@
         <v>46193.61403773148</v>
       </c>
       <c r="D59" s="8">
-        <v>46193.614040625005</v>
+        <v>46195.913108946756</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -5234,7 +5234,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46195.567961782406</v>
+        <v>46196.58119877314</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46195.56842914352</v>
+        <v>46196.58146922453</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46195.56824184028</v>
+        <v>46197.418882557875</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -5124,9 +5124,11 @@
       <c r="B64" s="5">
         <v>46073.63987194444</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46197.41887475694</v>
+      </c>
       <c r="D64" s="5">
-        <v>46193.564154085645</v>
+        <v>46197.418877118056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5234,7 +5236,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46196.58119877314</v>
+        <v>46197.50869553241</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="269">
   <si>
     <t>50001473 - MAPIMI</t>
   </si>
@@ -725,6 +725,12 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
   </si>
   <si>
     <t>Embalaje,Logistica:</t>
@@ -1438,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.63986869213</v>
+        <v>46073.47320202546</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.717724710645</v>
+        <v>46092.55105804398</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.839536643514</v>
+        <v>46134.67286997685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1487,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.63986902778</v>
+        <v>46073.473202361114</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.717694618055</v>
+        <v>46092.551027951384</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877865057875</v>
+        <v>46133.711198391204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1552,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.63986934027</v>
+        <v>46073.47320267362</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.717695127314</v>
+        <v>46092.55102846065</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71772585648</v>
+        <v>46092.55105918982</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1617,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.63986962963</v>
+        <v>46073.47320296297</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.717695555555</v>
+        <v>46092.55102888889</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71772572916</v>
+        <v>46092.551059062505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1682,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.639869942126</v>
+        <v>46073.47320327546</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.717695960644</v>
+        <v>46092.55102929398</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.78363827546</v>
+        <v>46100.6169716088</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1747,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.63987023148</v>
+        <v>46073.47320356482</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71769665509</v>
+        <v>46092.551029988426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71772622685</v>
+        <v>46092.55105956018</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1812,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.639870520834</v>
+        <v>46073.47320385417</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.64914818287</v>
+        <v>46128.4824815162</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.649159872686</v>
+        <v>46128.482493206015</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1865,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.63987082176</v>
+        <v>46073.47320415509</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.61935167824</v>
+        <v>46099.45268501157</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.619374120375</v>
+        <v>46099.4527074537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1930,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.63987108796</v>
+        <v>46073.4732044213</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.64913424768</v>
+        <v>46128.48246758102</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.64915</v>
+        <v>46128.48248333333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -1995,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.63987138889</v>
+        <v>46073.47320472222</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.779946180555</v>
+        <v>46107.613279513884</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.8394806713</v>
+        <v>46134.67281400463</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2044,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.63986841435</v>
+        <v>46073.473201747685</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55055525463</v>
+        <v>46097.38388858797</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.550571608794</v>
+        <v>46097.38390494213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2109,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.63986943287</v>
+        <v>46073.4732027662</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.77985594908</v>
+        <v>46107.613189282405</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.77987517361</v>
+        <v>46107.61320850694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2174,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.63987</v>
+        <v>46073.473203333335</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.550767719906</v>
+        <v>46097.38410105324</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.5507822338</v>
+        <v>46097.384115567125</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2239,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.6398705787</v>
+        <v>46073.473203912035</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.77992613426</v>
+        <v>46107.61325946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.77994740741</v>
+        <v>46107.61328074074</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2304,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.63987087963</v>
+        <v>46073.47320421296</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.780059386576</v>
+        <v>46107.61339271991</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.780072222224</v>
+        <v>46107.61340555556</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2357,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.63987116898</v>
+        <v>46073.47320450231</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.78000262732</v>
+        <v>46107.61333596065</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.780019328704</v>
+        <v>46107.61335266204</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2422,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.63987179398</v>
+        <v>46073.47320512732</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.550614884254</v>
+        <v>46097.3839482176</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.55063</v>
+        <v>46097.383963333334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2487,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.63987206019</v>
+        <v>46073.473205393515</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.619815949074</v>
+        <v>46099.4531492824</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.61983109954</v>
+        <v>46099.45316443287</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2552,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.63987269676</v>
+        <v>46073.47320603009</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.780038854165</v>
+        <v>46107.6133721875</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.83677627315</v>
+        <v>46134.67010960648</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2617,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.639868287035</v>
+        <v>46073.47320162037</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55083957176</v>
+        <v>46097.38417290509</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.64059725695</v>
+        <v>46197.47393059028</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2682,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.63986866898</v>
+        <v>46073.473202002315</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.60291127315</v>
+        <v>46112.43624460648</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.83959192129</v>
+        <v>46134.67292525463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2731,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.63986895833</v>
+        <v>46073.473202291665</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.78015736111</v>
+        <v>46107.61349069445</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.780284016204</v>
+        <v>46107.61361734953</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2796,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.78008822916</v>
+        <v>46107.6134215625</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.78008986111</v>
+        <v>46107.613423194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2857,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.63986952546</v>
+        <v>46073.4732028588</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.78014291667</v>
+        <v>46107.61347625</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.78014446759</v>
+        <v>46107.61347780093</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2918,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.639869861116</v>
+        <v>46073.473203194444</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.64901734954</v>
+        <v>46128.48235068287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.64903339121</v>
+        <v>46128.48236672454</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2983,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.63987017361</v>
+        <v>46073.47320350695</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.61991980324</v>
+        <v>46099.45325313657</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.61992293982</v>
+        <v>46099.45325627315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3044,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.649000590274</v>
+        <v>46128.48233392361</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.6490021412</v>
+        <v>46128.48233547454</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3105,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.639870810184</v>
+        <v>46073.47320414352</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.84297413194</v>
+        <v>46125.67630746528</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.84297541667</v>
+        <v>46125.67630875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3170,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.78179094907</v>
+        <v>46107.61512428241</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.781792395836</v>
+        <v>46107.615125729164</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3231,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.639868321756</v>
+        <v>46073.47320165509</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.78183342592</v>
+        <v>46107.615166759264</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.781834988426</v>
+        <v>46107.61516832176</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3292,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.63986865741</v>
+        <v>46073.47320199074</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.78100310185</v>
+        <v>46107.61433643519</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.781017974536</v>
+        <v>46107.61435130787</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3357,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.639868935184</v>
+        <v>46073.47320226852</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.55069820602</v>
+        <v>46097.38403153935</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.550699872685</v>
+        <v>46097.38403320602</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3418,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.78094795139</v>
+        <v>46107.614281284725</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.7809494213</v>
+        <v>46107.61428275463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3479,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.63986949074</v>
+        <v>46073.47320282407</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.780985590274</v>
+        <v>46107.61431892361</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.780987465274</v>
+        <v>46107.61432079861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3540,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.63986978009</v>
+        <v>46073.473203113426</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.550948819444</v>
+        <v>46097.38428215278</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.550965891205</v>
+        <v>46097.38429922453</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3605,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.63987009259</v>
+        <v>46073.47320342592</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.550895844906</v>
+        <v>46097.38422917824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.550897141205</v>
+        <v>46097.384230474534</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3666,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.63987039352</v>
+        <v>46073.473203726855</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.550933923616</v>
+        <v>46097.384267256944</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.55093533565</v>
+        <v>46097.38426866898</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3727,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.63987067129</v>
+        <v>46073.47320400463</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.839630381946</v>
+        <v>46134.672963715275</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3774,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.639870983796</v>
+        <v>46073.473204317124</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.51873575231</v>
+        <v>46114.35206908565</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51875664352</v>
+        <v>46114.35208997685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3839,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.6398703125</v>
+        <v>46073.47320364583</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.79026576389</v>
+        <v>46114.62359909722</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.79028366898</v>
+        <v>46114.62361700232</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3904,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.679795104166</v>
+        <v>46090.513128437495</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79031591435</v>
+        <v>46114.62364924769</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79033271991</v>
+        <v>46114.623666053245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3967,11 +3973,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.67984755787</v>
+        <v>46090.513180891205</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.56824368055</v>
+        <v>46195.401577013894</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4034,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.639870659725</v>
+        <v>46073.47320399305</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.70373234954</v>
+        <v>46122.537065682875</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.70375010416</v>
+        <v>46122.5370834375</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4081,13 +4087,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.6398709375</v>
+        <v>46073.473204270835</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.65644733796</v>
+        <v>46122.4897806713</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.65646496528</v>
+        <v>46122.489798298615</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4146,13 +4152,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.639871203704</v>
+        <v>46073.47320453703</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.703715509255</v>
+        <v>46122.5370488426</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.70373212963</v>
+        <v>46122.537065462966</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4211,11 +4217,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.6398714699</v>
+        <v>46073.473204803246</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.913107650464</v>
+        <v>46195.7464409838</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4258,13 +4264,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.63987175926</v>
+        <v>46073.473205092596</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.49427167824</v>
+        <v>46128.327605011575</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.49428587963</v>
+        <v>46128.32761921296</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4323,13 +4329,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.63987204861</v>
+        <v>46073.473205381946</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.881092916665</v>
+        <v>46191.71442625</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.67647228009</v>
+        <v>46194.50980561343</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4388,13 +4394,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.63987233797</v>
+        <v>46073.4732056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.91309923611</v>
+        <v>46195.746432569445</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.9131012963</v>
+        <v>46195.74643462963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4451,11 +4457,11 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.639872604166</v>
+        <v>46073.473205937495</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46193.564339317134</v>
+        <v>46193.39767265046</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,13 +4504,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.639872858796</v>
+        <v>46073.47320619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.56431931713</v>
+        <v>46193.39765265046</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.6765421412</v>
+        <v>46194.50987547454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4563,13 +4569,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.64907399306</v>
+        <v>46128.48240732639</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.64908931713</v>
+        <v>46128.482422650464</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4626,13 +4632,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.639869606486</v>
+        <v>46073.473202939815</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.56433421296</v>
+        <v>46193.39766754629</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.676592627315</v>
+        <v>46194.50992596065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4691,13 +4697,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.639869907405</v>
+        <v>46073.47320324074</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.656911909726</v>
+        <v>46122.490245243054</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.656931226855</v>
+        <v>46122.49026456018</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4754,11 +4760,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.639870196756</v>
+        <v>46073.47320353009</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46197.418882557875</v>
+        <v>46197.2522158912</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4801,13 +4807,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.61403773148</v>
+        <v>46193.447371064816</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.913108946756</v>
+        <v>46195.74644228009</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4866,13 +4872,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.63987084491</v>
+        <v>46073.47320417824</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.61407924768</v>
+        <v>46193.44741258102</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.61408086805</v>
+        <v>46193.44741420139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4929,13 +4935,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.6140899537</v>
+        <v>46193.44742328704</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.61409614583</v>
+        <v>46193.447429479165</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -4994,13 +5000,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.63987140046</v>
+        <v>46073.4732047338</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61410039352</v>
+        <v>46193.44743372685</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.61410226852</v>
+        <v>46193.44743560185</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5059,13 +5065,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.63987167824</v>
+        <v>46073.47320501157</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.56823568287</v>
+        <v>46195.401569016205</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.56823783564</v>
+        <v>46195.401571168986</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5122,13 +5128,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.63987194444</v>
+        <v>46073.473205277776</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.41887475694</v>
+        <v>46197.25220809028</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.418877118056</v>
+        <v>46197.25221045139</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5185,11 +5191,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.63986877315</v>
+        <v>46073.473202106485</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46090.69097142361</v>
+        <v>46197.53143545139</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5232,11 +5238,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.50869553241</v>
+        <v>46197.53334677083</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5245,10 +5251,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>37</v>
+        <v>239</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5270,7 +5276,7 @@
         <v>170</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q66" s="5">
         <v>46013</v>
@@ -5290,17 +5296,19 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.63986957176</v>
-      </c>
-      <c r="C67" s="9"/>
+        <v>46073.473202905094</v>
+      </c>
+      <c r="C67" s="8">
+        <v>46197.531424479166</v>
+      </c>
       <c r="D67" s="8">
-        <v>46128.64913983796</v>
+        <v>46197.53142733796</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5328,10 +5336,10 @@
         <v>234</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q67" s="8">
         <v>46017</v>
@@ -5351,17 +5359,17 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.63986991898</v>
+        <v>46073.47320325232</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46196.58146922453</v>
+        <v>46197.531434247685</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5389,10 +5397,10 @@
         <v>234</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q68" s="5">
         <v>46020</v>
@@ -5412,17 +5420,17 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.63987025463</v>
+        <v>46073.473203587964</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46090.8459034375</v>
+        <v>46090.67923677083</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5450,10 +5458,10 @@
         <v>234</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q69" s="8">
         <v>46021</v>
@@ -5473,17 +5481,17 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.63987059028</v>
+        <v>46073.47320392361</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.641527106476</v>
+        <v>46083.47486043982</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5507,7 +5515,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5520,26 +5528,26 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.639870914354</v>
+        <v>46073.47320424768</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.845954131946</v>
+        <v>46090.679287465275</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I71" s="8">
         <v>46022</v>
@@ -5557,13 +5565,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q71" s="8">
         <v>46022</v>
@@ -5583,26 +5591,26 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.639871273146</v>
+        <v>46073.47320460648</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.77993362269</v>
+        <v>46107.61326695602</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>257</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="I72" s="5">
         <v>46022</v>
@@ -5620,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46022</v>
@@ -5646,17 +5654,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.680186840276</v>
+        <v>46090.51352017361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.68746959491</v>
+        <v>46090.52080292824</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5680,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5693,17 +5701,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.68032269676</v>
+        <v>46090.51365603009</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.84604261574</v>
+        <v>46090.679375949076</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5730,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46024</v>
@@ -5756,17 +5764,17 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.68039148148</v>
+        <v>46090.51372481481</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.84603971065</v>
+        <v>46090.67937304398</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5793,13 +5801,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="8">
         <v>46035</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1444,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.47320202546</v>
+        <v>46073.63986869213</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55105804398</v>
+        <v>46092.717724710645</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.67286997685</v>
+        <v>46134.839536643514</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1493,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.473202361114</v>
+        <v>46073.63986902778</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.551027951384</v>
+        <v>46092.717694618055</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.711198391204</v>
+        <v>46133.877865057875</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1558,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.47320267362</v>
+        <v>46073.63986934027</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55102846065</v>
+        <v>46092.717695127314</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55105918982</v>
+        <v>46092.71772585648</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1623,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.47320296297</v>
+        <v>46073.63986962963</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55102888889</v>
+        <v>46092.717695555555</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.551059062505</v>
+        <v>46092.71772572916</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1688,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.47320327546</v>
+        <v>46073.639869942126</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55102929398</v>
+        <v>46092.717695960644</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6169716088</v>
+        <v>46100.78363827546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1753,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.47320356482</v>
+        <v>46073.63987023148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.551029988426</v>
+        <v>46092.71769665509</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55105956018</v>
+        <v>46092.71772622685</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1818,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.47320385417</v>
+        <v>46073.639870520834</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.4824815162</v>
+        <v>46128.64914818287</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.482493206015</v>
+        <v>46128.649159872686</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1871,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.47320415509</v>
+        <v>46073.63987082176</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.45268501157</v>
+        <v>46099.61935167824</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.4527074537</v>
+        <v>46099.619374120375</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1936,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.4732044213</v>
+        <v>46073.63987108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.48246758102</v>
+        <v>46128.64913424768</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.48248333333</v>
+        <v>46128.64915</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2001,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.47320472222</v>
+        <v>46073.63987138889</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.613279513884</v>
+        <v>46107.779946180555</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.67281400463</v>
+        <v>46134.8394806713</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2050,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.473201747685</v>
+        <v>46073.63986841435</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38388858797</v>
+        <v>46097.55055525463</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38390494213</v>
+        <v>46097.550571608794</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2115,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.4732027662</v>
+        <v>46073.63986943287</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.613189282405</v>
+        <v>46107.77985594908</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.61320850694</v>
+        <v>46107.77987517361</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2180,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.473203333335</v>
+        <v>46073.63987</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38410105324</v>
+        <v>46097.550767719906</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.384115567125</v>
+        <v>46097.5507822338</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2245,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.473203912035</v>
+        <v>46073.6398705787</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.61325946759</v>
+        <v>46107.77992613426</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.61328074074</v>
+        <v>46107.77994740741</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2310,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.47320421296</v>
+        <v>46073.63987087963</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.61339271991</v>
+        <v>46107.780059386576</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.61340555556</v>
+        <v>46107.780072222224</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.47320450231</v>
+        <v>46073.63987116898</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.61333596065</v>
+        <v>46107.78000262732</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.61335266204</v>
+        <v>46107.780019328704</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2428,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.47320512732</v>
+        <v>46073.63987179398</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3839482176</v>
+        <v>46097.550614884254</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.383963333334</v>
+        <v>46097.55063</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2493,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.473205393515</v>
+        <v>46073.63987206019</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.4531492824</v>
+        <v>46099.619815949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.45316443287</v>
+        <v>46099.61983109954</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2558,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.47320603009</v>
+        <v>46073.63987269676</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.6133721875</v>
+        <v>46107.780038854165</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.67010960648</v>
+        <v>46134.83677627315</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2623,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.47320162037</v>
+        <v>46073.639868287035</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38417290509</v>
+        <v>46097.55083957176</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.47393059028</v>
+        <v>46197.64059725695</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.473202002315</v>
+        <v>46073.63986866898</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.43624460648</v>
+        <v>46112.60291127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.67292525463</v>
+        <v>46134.83959192129</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2737,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.473202291665</v>
+        <v>46073.63986895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.61349069445</v>
+        <v>46107.78015736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.61361734953</v>
+        <v>46107.780284016204</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2802,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.6134215625</v>
+        <v>46107.78008822916</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.613423194445</v>
+        <v>46107.78008986111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2863,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.4732028588</v>
+        <v>46073.63986952546</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.61347625</v>
+        <v>46107.78014291667</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.61347780093</v>
+        <v>46107.78014446759</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2924,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.473203194444</v>
+        <v>46073.639869861116</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.48235068287</v>
+        <v>46128.64901734954</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.48236672454</v>
+        <v>46128.64903339121</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2989,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.47320350695</v>
+        <v>46073.63987017361</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.45325313657</v>
+        <v>46099.61991980324</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.45325627315</v>
+        <v>46099.61992293982</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3050,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.48233392361</v>
+        <v>46128.649000590274</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.48233547454</v>
+        <v>46128.6490021412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3111,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.47320414352</v>
+        <v>46073.639870810184</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.67630746528</v>
+        <v>46125.84297413194</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.67630875</v>
+        <v>46125.84297541667</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3176,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.61512428241</v>
+        <v>46107.78179094907</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.615125729164</v>
+        <v>46107.781792395836</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3237,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.47320165509</v>
+        <v>46073.639868321756</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.615166759264</v>
+        <v>46107.78183342592</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.61516832176</v>
+        <v>46107.781834988426</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3298,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.47320199074</v>
+        <v>46073.63986865741</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.61433643519</v>
+        <v>46107.78100310185</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.61435130787</v>
+        <v>46107.781017974536</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3363,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.47320226852</v>
+        <v>46073.639868935184</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38403153935</v>
+        <v>46097.55069820602</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38403320602</v>
+        <v>46097.550699872685</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3424,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.614281284725</v>
+        <v>46107.78094795139</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.61428275463</v>
+        <v>46107.7809494213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3485,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.47320282407</v>
+        <v>46073.63986949074</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.61431892361</v>
+        <v>46107.780985590274</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.61432079861</v>
+        <v>46107.780987465274</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3546,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.473203113426</v>
+        <v>46073.63986978009</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38428215278</v>
+        <v>46097.550948819444</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38429922453</v>
+        <v>46097.550965891205</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3611,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.47320342592</v>
+        <v>46073.63987009259</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.38422917824</v>
+        <v>46097.550895844906</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.384230474534</v>
+        <v>46097.550897141205</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3672,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.473203726855</v>
+        <v>46073.63987039352</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.384267256944</v>
+        <v>46097.550933923616</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.38426866898</v>
+        <v>46097.55093533565</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3733,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.47320400463</v>
+        <v>46073.63987067129</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.672963715275</v>
+        <v>46134.839630381946</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3780,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.473204317124</v>
+        <v>46073.639870983796</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.35206908565</v>
+        <v>46114.51873575231</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.35208997685</v>
+        <v>46114.51875664352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3845,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.47320364583</v>
+        <v>46073.6398703125</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.62359909722</v>
+        <v>46114.79026576389</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.62361700232</v>
+        <v>46114.79028366898</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3910,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.513128437495</v>
+        <v>46090.679795104166</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.62364924769</v>
+        <v>46114.79031591435</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.623666053245</v>
+        <v>46114.79033271991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3973,11 +3973,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.513180891205</v>
+        <v>46090.67984755787</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.401577013894</v>
+        <v>46195.56824368055</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4034,13 +4034,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.47320399305</v>
+        <v>46073.639870659725</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.537065682875</v>
+        <v>46122.70373234954</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.5370834375</v>
+        <v>46122.70375010416</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4087,13 +4087,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.473204270835</v>
+        <v>46073.6398709375</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.4897806713</v>
+        <v>46122.65644733796</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.489798298615</v>
+        <v>46122.65646496528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4152,13 +4152,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.47320453703</v>
+        <v>46073.639871203704</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.5370488426</v>
+        <v>46122.703715509255</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.537065462966</v>
+        <v>46122.70373212963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4217,11 +4217,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.473204803246</v>
+        <v>46073.6398714699</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.7464409838</v>
+        <v>46195.913107650464</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4264,13 +4264,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.473205092596</v>
+        <v>46073.63987175926</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.327605011575</v>
+        <v>46128.49427167824</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.32761921296</v>
+        <v>46128.49428587963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4329,13 +4329,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.473205381946</v>
+        <v>46073.63987204861</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.71442625</v>
+        <v>46191.881092916665</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.50980561343</v>
+        <v>46194.67647228009</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4394,13 +4394,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4732056713</v>
+        <v>46073.63987233797</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.746432569445</v>
+        <v>46195.91309923611</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.74643462963</v>
+        <v>46195.9131012963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4457,11 +4457,11 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.473205937495</v>
+        <v>46073.639872604166</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46193.39767265046</v>
+        <v>46193.564339317134</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4504,13 +4504,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.47320619213</v>
+        <v>46073.639872858796</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.39765265046</v>
+        <v>46193.56431931713</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.50987547454</v>
+        <v>46194.6765421412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4569,13 +4569,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48240732639</v>
+        <v>46128.64907399306</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.482422650464</v>
+        <v>46128.64908931713</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4632,13 +4632,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.473202939815</v>
+        <v>46073.639869606486</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.39766754629</v>
+        <v>46193.56433421296</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.50992596065</v>
+        <v>46194.676592627315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4697,13 +4697,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.47320324074</v>
+        <v>46073.639869907405</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.490245243054</v>
+        <v>46122.656911909726</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.49026456018</v>
+        <v>46122.656931226855</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4760,11 +4760,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.47320353009</v>
+        <v>46073.639870196756</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46197.2522158912</v>
+        <v>46197.418882557875</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4807,13 +4807,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.447371064816</v>
+        <v>46193.61403773148</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.74644228009</v>
+        <v>46195.913108946756</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4872,13 +4872,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.47320417824</v>
+        <v>46073.63987084491</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.44741258102</v>
+        <v>46193.61407924768</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.44741420139</v>
+        <v>46193.61408086805</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4935,13 +4935,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.44742328704</v>
+        <v>46193.6140899537</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.447429479165</v>
+        <v>46193.61409614583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5000,13 +5000,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4732047338</v>
+        <v>46073.63987140046</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.44743372685</v>
+        <v>46193.61410039352</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.44743560185</v>
+        <v>46193.61410226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5065,13 +5065,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.47320501157</v>
+        <v>46073.63987167824</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.401569016205</v>
+        <v>46195.56823568287</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.401571168986</v>
+        <v>46195.56823783564</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5128,13 +5128,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.473205277776</v>
+        <v>46073.63987194444</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.25220809028</v>
+        <v>46197.41887475694</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.25221045139</v>
+        <v>46197.418877118056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5191,11 +5191,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.473202106485</v>
+        <v>46073.63986877315</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.53143545139</v>
+        <v>46197.708056944444</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5238,11 +5238,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.53334677083</v>
+        <v>46197.72072909722</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5299,13 +5299,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.473202905094</v>
+        <v>46073.63986957176</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.531424479166</v>
+        <v>46197.69809114584</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.53142733796</v>
+        <v>46197.698094004634</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5362,11 +5362,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.47320325232</v>
-      </c>
-      <c r="C68" s="6"/>
+        <v>46073.63986991898</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46197.70804978009</v>
+      </c>
       <c r="D68" s="5">
-        <v>46197.531434247685</v>
+        <v>46197.70805155093</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5423,11 +5425,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.473203587964</v>
+        <v>46073.63987025463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46090.67923677083</v>
+        <v>46197.70805605324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5484,11 +5486,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.47320392361</v>
+        <v>46073.63987059028</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.47486043982</v>
+        <v>46083.641527106476</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>
@@ -5531,11 +5533,11 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.47320424768</v>
+        <v>46073.639870914354</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.679287465275</v>
+        <v>46090.845954131946</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5594,11 +5596,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.47320460648</v>
+        <v>46073.639871273146</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.61326695602</v>
+        <v>46107.77993362269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5657,11 +5659,11 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.51352017361</v>
+        <v>46090.680186840276</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.52080292824</v>
+        <v>46090.68746959491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5704,11 +5706,11 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.51365603009</v>
+        <v>46090.68032269676</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.679375949076</v>
+        <v>46090.84604261574</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5767,11 +5769,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.51372481481</v>
+        <v>46090.68039148148</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.67937304398</v>
+        <v>46090.84603971065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1444,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.63986869213</v>
+        <v>46073.47320202546</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.717724710645</v>
+        <v>46092.55105804398</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.839536643514</v>
+        <v>46134.67286997685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1493,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.63986902778</v>
+        <v>46073.473202361114</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.717694618055</v>
+        <v>46092.551027951384</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877865057875</v>
+        <v>46133.711198391204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1558,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.63986934027</v>
+        <v>46073.47320267362</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.717695127314</v>
+        <v>46092.55102846065</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71772585648</v>
+        <v>46092.55105918982</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1623,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.63986962963</v>
+        <v>46073.47320296297</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.717695555555</v>
+        <v>46092.55102888889</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71772572916</v>
+        <v>46092.551059062505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1688,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.639869942126</v>
+        <v>46073.47320327546</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.717695960644</v>
+        <v>46092.55102929398</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.78363827546</v>
+        <v>46100.6169716088</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1753,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.63987023148</v>
+        <v>46073.47320356482</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71769665509</v>
+        <v>46092.551029988426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71772622685</v>
+        <v>46092.55105956018</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1818,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.639870520834</v>
+        <v>46073.47320385417</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.64914818287</v>
+        <v>46128.4824815162</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.649159872686</v>
+        <v>46128.482493206015</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1871,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.63987082176</v>
+        <v>46073.47320415509</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.61935167824</v>
+        <v>46099.45268501157</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.619374120375</v>
+        <v>46099.4527074537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1936,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.63987108796</v>
+        <v>46073.4732044213</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.64913424768</v>
+        <v>46128.48246758102</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.64915</v>
+        <v>46128.48248333333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2001,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.63987138889</v>
+        <v>46073.47320472222</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.779946180555</v>
+        <v>46107.613279513884</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.8394806713</v>
+        <v>46134.67281400463</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2050,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.63986841435</v>
+        <v>46073.473201747685</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55055525463</v>
+        <v>46097.38388858797</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.550571608794</v>
+        <v>46097.38390494213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2115,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.63986943287</v>
+        <v>46073.4732027662</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.77985594908</v>
+        <v>46107.613189282405</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.77987517361</v>
+        <v>46107.61320850694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2180,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.63987</v>
+        <v>46073.473203333335</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.550767719906</v>
+        <v>46097.38410105324</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.5507822338</v>
+        <v>46097.384115567125</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2245,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.6398705787</v>
+        <v>46073.473203912035</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.77992613426</v>
+        <v>46107.61325946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.77994740741</v>
+        <v>46107.61328074074</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2310,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.63987087963</v>
+        <v>46073.47320421296</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.780059386576</v>
+        <v>46107.61339271991</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.780072222224</v>
+        <v>46107.61340555556</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.63987116898</v>
+        <v>46073.47320450231</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.78000262732</v>
+        <v>46107.61333596065</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.780019328704</v>
+        <v>46107.61335266204</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2428,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.63987179398</v>
+        <v>46073.47320512732</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.550614884254</v>
+        <v>46097.3839482176</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.55063</v>
+        <v>46097.383963333334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2493,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.63987206019</v>
+        <v>46073.473205393515</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.619815949074</v>
+        <v>46099.4531492824</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.61983109954</v>
+        <v>46099.45316443287</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2558,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.63987269676</v>
+        <v>46073.47320603009</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.780038854165</v>
+        <v>46107.6133721875</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.83677627315</v>
+        <v>46134.67010960648</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2623,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.639868287035</v>
+        <v>46073.47320162037</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55083957176</v>
+        <v>46097.38417290509</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.64059725695</v>
+        <v>46197.47393059028</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.63986866898</v>
+        <v>46073.473202002315</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.60291127315</v>
+        <v>46112.43624460648</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.83959192129</v>
+        <v>46134.67292525463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2737,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.63986895833</v>
+        <v>46073.473202291665</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.78015736111</v>
+        <v>46107.61349069445</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.780284016204</v>
+        <v>46107.61361734953</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2802,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.78008822916</v>
+        <v>46107.6134215625</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.78008986111</v>
+        <v>46107.613423194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2863,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.63986952546</v>
+        <v>46073.4732028588</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.78014291667</v>
+        <v>46107.61347625</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.78014446759</v>
+        <v>46107.61347780093</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2924,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.639869861116</v>
+        <v>46073.473203194444</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.64901734954</v>
+        <v>46128.48235068287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.64903339121</v>
+        <v>46128.48236672454</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2989,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.63987017361</v>
+        <v>46073.47320350695</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.61991980324</v>
+        <v>46099.45325313657</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.61992293982</v>
+        <v>46099.45325627315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3050,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.649000590274</v>
+        <v>46128.48233392361</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.6490021412</v>
+        <v>46128.48233547454</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3111,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.639870810184</v>
+        <v>46073.47320414352</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.84297413194</v>
+        <v>46125.67630746528</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.84297541667</v>
+        <v>46125.67630875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3176,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.78179094907</v>
+        <v>46107.61512428241</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.781792395836</v>
+        <v>46107.615125729164</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3237,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.639868321756</v>
+        <v>46073.47320165509</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.78183342592</v>
+        <v>46107.615166759264</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.781834988426</v>
+        <v>46107.61516832176</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3298,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.63986865741</v>
+        <v>46073.47320199074</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.78100310185</v>
+        <v>46107.61433643519</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.781017974536</v>
+        <v>46107.61435130787</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3363,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.639868935184</v>
+        <v>46073.47320226852</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.55069820602</v>
+        <v>46097.38403153935</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.550699872685</v>
+        <v>46097.38403320602</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3424,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.78094795139</v>
+        <v>46107.614281284725</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.7809494213</v>
+        <v>46107.61428275463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3485,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.63986949074</v>
+        <v>46073.47320282407</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.780985590274</v>
+        <v>46107.61431892361</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.780987465274</v>
+        <v>46107.61432079861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3546,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.63986978009</v>
+        <v>46073.473203113426</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.550948819444</v>
+        <v>46097.38428215278</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.550965891205</v>
+        <v>46097.38429922453</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3611,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.63987009259</v>
+        <v>46073.47320342592</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.550895844906</v>
+        <v>46097.38422917824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.550897141205</v>
+        <v>46097.384230474534</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3672,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.63987039352</v>
+        <v>46073.473203726855</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.550933923616</v>
+        <v>46097.384267256944</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.55093533565</v>
+        <v>46097.38426866898</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3733,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.63987067129</v>
+        <v>46073.47320400463</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.839630381946</v>
+        <v>46134.672963715275</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3780,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.639870983796</v>
+        <v>46073.473204317124</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.51873575231</v>
+        <v>46114.35206908565</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51875664352</v>
+        <v>46114.35208997685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3845,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.6398703125</v>
+        <v>46073.47320364583</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.79026576389</v>
+        <v>46114.62359909722</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.79028366898</v>
+        <v>46114.62361700232</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3910,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.679795104166</v>
+        <v>46090.513128437495</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79031591435</v>
+        <v>46114.62364924769</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79033271991</v>
+        <v>46114.623666053245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3973,11 +3973,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.67984755787</v>
+        <v>46090.513180891205</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.56824368055</v>
+        <v>46195.401577013894</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4034,13 +4034,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.639870659725</v>
+        <v>46073.47320399305</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.70373234954</v>
+        <v>46122.537065682875</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.70375010416</v>
+        <v>46122.5370834375</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4087,13 +4087,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.6398709375</v>
+        <v>46073.473204270835</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.65644733796</v>
+        <v>46122.4897806713</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.65646496528</v>
+        <v>46122.489798298615</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4152,13 +4152,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.639871203704</v>
+        <v>46073.47320453703</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.703715509255</v>
+        <v>46122.5370488426</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.70373212963</v>
+        <v>46122.537065462966</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4217,11 +4217,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.6398714699</v>
+        <v>46073.473204803246</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.913107650464</v>
+        <v>46195.7464409838</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4264,13 +4264,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.63987175926</v>
+        <v>46073.473205092596</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.49427167824</v>
+        <v>46128.327605011575</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.49428587963</v>
+        <v>46128.32761921296</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4329,13 +4329,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.63987204861</v>
+        <v>46073.473205381946</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.881092916665</v>
+        <v>46191.71442625</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.67647228009</v>
+        <v>46194.50980561343</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4394,13 +4394,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.63987233797</v>
+        <v>46073.4732056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.91309923611</v>
+        <v>46195.746432569445</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.9131012963</v>
+        <v>46195.74643462963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4457,11 +4457,11 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.639872604166</v>
+        <v>46073.473205937495</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46193.564339317134</v>
+        <v>46193.39767265046</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4504,13 +4504,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.639872858796</v>
+        <v>46073.47320619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.56431931713</v>
+        <v>46193.39765265046</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.6765421412</v>
+        <v>46194.50987547454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4569,13 +4569,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.64907399306</v>
+        <v>46128.48240732639</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.64908931713</v>
+        <v>46128.482422650464</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4632,13 +4632,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.639869606486</v>
+        <v>46073.473202939815</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.56433421296</v>
+        <v>46193.39766754629</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.676592627315</v>
+        <v>46194.50992596065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4697,13 +4697,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.639869907405</v>
+        <v>46073.47320324074</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.656911909726</v>
+        <v>46122.490245243054</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.656931226855</v>
+        <v>46122.49026456018</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4760,11 +4760,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.639870196756</v>
+        <v>46073.47320353009</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46197.418882557875</v>
+        <v>46197.2522158912</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4807,13 +4807,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.61403773148</v>
+        <v>46193.447371064816</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.913108946756</v>
+        <v>46195.74644228009</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4872,13 +4872,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.63987084491</v>
+        <v>46073.47320417824</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.61407924768</v>
+        <v>46193.44741258102</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.61408086805</v>
+        <v>46193.44741420139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4935,13 +4935,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.6140899537</v>
+        <v>46193.44742328704</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.61409614583</v>
+        <v>46193.447429479165</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5000,13 +5000,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.63987140046</v>
+        <v>46073.4732047338</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61410039352</v>
+        <v>46193.44743372685</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.61410226852</v>
+        <v>46193.44743560185</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5065,13 +5065,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.63987167824</v>
+        <v>46073.47320501157</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.56823568287</v>
+        <v>46195.401569016205</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.56823783564</v>
+        <v>46195.401571168986</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5128,13 +5128,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.63987194444</v>
+        <v>46073.473205277776</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.41887475694</v>
+        <v>46197.25220809028</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.418877118056</v>
+        <v>46197.25221045139</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5191,11 +5191,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.63986877315</v>
+        <v>46073.473202106485</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.708056944444</v>
+        <v>46197.54139027778</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5238,11 +5238,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.72072909722</v>
+        <v>46197.55406243056</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5299,13 +5299,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.63986957176</v>
+        <v>46073.473202905094</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.69809114584</v>
+        <v>46197.531424479166</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.698094004634</v>
+        <v>46197.53142733796</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5362,13 +5362,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.63986991898</v>
+        <v>46073.47320325232</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.70804978009</v>
+        <v>46197.54138311342</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.70805155093</v>
+        <v>46197.54138488426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5425,11 +5425,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.63987025463</v>
+        <v>46073.473203587964</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.70805605324</v>
+        <v>46197.54138938658</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5486,11 +5486,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.63987059028</v>
+        <v>46073.47320392361</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.641527106476</v>
+        <v>46083.47486043982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>
@@ -5533,11 +5533,11 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.639870914354</v>
+        <v>46073.47320424768</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.845954131946</v>
+        <v>46090.679287465275</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5596,11 +5596,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.639871273146</v>
+        <v>46073.47320460648</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.77993362269</v>
+        <v>46107.61326695602</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5659,11 +5659,11 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.680186840276</v>
+        <v>46090.51352017361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.68746959491</v>
+        <v>46090.52080292824</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5706,11 +5706,11 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.68032269676</v>
+        <v>46090.51365603009</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.84604261574</v>
+        <v>46090.679375949076</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5769,11 +5769,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.68039148148</v>
+        <v>46090.51372481481</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.84603971065</v>
+        <v>46090.67937304398</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1444,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.47320202546</v>
+        <v>46073.63986869213</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55105804398</v>
+        <v>46092.717724710645</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.67286997685</v>
+        <v>46134.839536643514</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1493,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.473202361114</v>
+        <v>46073.63986902778</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.551027951384</v>
+        <v>46092.717694618055</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.711198391204</v>
+        <v>46133.877865057875</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1558,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.47320267362</v>
+        <v>46073.63986934027</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55102846065</v>
+        <v>46092.717695127314</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55105918982</v>
+        <v>46092.71772585648</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1623,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.47320296297</v>
+        <v>46073.63986962963</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55102888889</v>
+        <v>46092.717695555555</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.551059062505</v>
+        <v>46092.71772572916</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1688,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.47320327546</v>
+        <v>46073.639869942126</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55102929398</v>
+        <v>46092.717695960644</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6169716088</v>
+        <v>46100.78363827546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1753,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.47320356482</v>
+        <v>46073.63987023148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.551029988426</v>
+        <v>46092.71769665509</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55105956018</v>
+        <v>46092.71772622685</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1818,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.47320385417</v>
+        <v>46073.639870520834</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.4824815162</v>
+        <v>46128.64914818287</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.482493206015</v>
+        <v>46128.649159872686</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1871,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.47320415509</v>
+        <v>46073.63987082176</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.45268501157</v>
+        <v>46099.61935167824</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.4527074537</v>
+        <v>46099.619374120375</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1936,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.4732044213</v>
+        <v>46073.63987108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.48246758102</v>
+        <v>46128.64913424768</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.48248333333</v>
+        <v>46128.64915</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2001,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.47320472222</v>
+        <v>46073.63987138889</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.613279513884</v>
+        <v>46107.779946180555</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.67281400463</v>
+        <v>46134.8394806713</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2050,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.473201747685</v>
+        <v>46073.63986841435</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38388858797</v>
+        <v>46097.55055525463</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38390494213</v>
+        <v>46097.550571608794</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2115,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.4732027662</v>
+        <v>46073.63986943287</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.613189282405</v>
+        <v>46107.77985594908</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.61320850694</v>
+        <v>46107.77987517361</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2180,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.473203333335</v>
+        <v>46073.63987</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38410105324</v>
+        <v>46097.550767719906</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.384115567125</v>
+        <v>46097.5507822338</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2245,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.473203912035</v>
+        <v>46073.6398705787</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.61325946759</v>
+        <v>46107.77992613426</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.61328074074</v>
+        <v>46107.77994740741</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2310,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.47320421296</v>
+        <v>46073.63987087963</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.61339271991</v>
+        <v>46107.780059386576</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.61340555556</v>
+        <v>46107.780072222224</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.47320450231</v>
+        <v>46073.63987116898</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.61333596065</v>
+        <v>46107.78000262732</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.61335266204</v>
+        <v>46107.780019328704</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2428,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.47320512732</v>
+        <v>46073.63987179398</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3839482176</v>
+        <v>46097.550614884254</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.383963333334</v>
+        <v>46097.55063</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2493,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.473205393515</v>
+        <v>46073.63987206019</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.4531492824</v>
+        <v>46099.619815949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.45316443287</v>
+        <v>46099.61983109954</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2558,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.47320603009</v>
+        <v>46073.63987269676</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.6133721875</v>
+        <v>46107.780038854165</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.67010960648</v>
+        <v>46134.83677627315</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2623,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.47320162037</v>
+        <v>46073.639868287035</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38417290509</v>
+        <v>46097.55083957176</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.47393059028</v>
+        <v>46197.64059725695</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.473202002315</v>
+        <v>46073.63986866898</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.43624460648</v>
+        <v>46112.60291127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.67292525463</v>
+        <v>46134.83959192129</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2737,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.473202291665</v>
+        <v>46073.63986895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.61349069445</v>
+        <v>46107.78015736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.61361734953</v>
+        <v>46107.780284016204</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2802,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.6134215625</v>
+        <v>46107.78008822916</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.613423194445</v>
+        <v>46107.78008986111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2863,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.4732028588</v>
+        <v>46073.63986952546</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.61347625</v>
+        <v>46107.78014291667</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.61347780093</v>
+        <v>46107.78014446759</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2924,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.473203194444</v>
+        <v>46073.639869861116</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.48235068287</v>
+        <v>46128.64901734954</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.48236672454</v>
+        <v>46128.64903339121</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2989,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.47320350695</v>
+        <v>46073.63987017361</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.45325313657</v>
+        <v>46099.61991980324</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.45325627315</v>
+        <v>46099.61992293982</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3050,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.48233392361</v>
+        <v>46128.649000590274</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.48233547454</v>
+        <v>46128.6490021412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3111,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.47320414352</v>
+        <v>46073.639870810184</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.67630746528</v>
+        <v>46125.84297413194</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.67630875</v>
+        <v>46125.84297541667</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3176,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.61512428241</v>
+        <v>46107.78179094907</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.615125729164</v>
+        <v>46107.781792395836</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3237,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.47320165509</v>
+        <v>46073.639868321756</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.615166759264</v>
+        <v>46107.78183342592</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.61516832176</v>
+        <v>46107.781834988426</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3298,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.47320199074</v>
+        <v>46073.63986865741</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.61433643519</v>
+        <v>46107.78100310185</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.61435130787</v>
+        <v>46107.781017974536</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3363,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.47320226852</v>
+        <v>46073.639868935184</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38403153935</v>
+        <v>46097.55069820602</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38403320602</v>
+        <v>46097.550699872685</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3424,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.614281284725</v>
+        <v>46107.78094795139</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.61428275463</v>
+        <v>46107.7809494213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3485,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.47320282407</v>
+        <v>46073.63986949074</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.61431892361</v>
+        <v>46107.780985590274</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.61432079861</v>
+        <v>46107.780987465274</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3546,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.473203113426</v>
+        <v>46073.63986978009</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38428215278</v>
+        <v>46097.550948819444</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38429922453</v>
+        <v>46097.550965891205</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3611,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.47320342592</v>
+        <v>46073.63987009259</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.38422917824</v>
+        <v>46097.550895844906</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.384230474534</v>
+        <v>46097.550897141205</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3672,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.473203726855</v>
+        <v>46073.63987039352</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.384267256944</v>
+        <v>46097.550933923616</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.38426866898</v>
+        <v>46097.55093533565</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3733,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.47320400463</v>
+        <v>46073.63987067129</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.672963715275</v>
+        <v>46134.839630381946</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3780,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.473204317124</v>
+        <v>46073.639870983796</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.35206908565</v>
+        <v>46114.51873575231</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.35208997685</v>
+        <v>46114.51875664352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3845,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.47320364583</v>
+        <v>46073.6398703125</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.62359909722</v>
+        <v>46114.79026576389</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.62361700232</v>
+        <v>46114.79028366898</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3910,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.513128437495</v>
+        <v>46090.679795104166</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.62364924769</v>
+        <v>46114.79031591435</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.623666053245</v>
+        <v>46114.79033271991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3973,11 +3973,11 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.513180891205</v>
+        <v>46090.67984755787</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46195.401577013894</v>
+        <v>46195.56824368055</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4034,13 +4034,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.47320399305</v>
+        <v>46073.639870659725</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.537065682875</v>
+        <v>46122.70373234954</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.5370834375</v>
+        <v>46122.70375010416</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4087,13 +4087,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.473204270835</v>
+        <v>46073.6398709375</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.4897806713</v>
+        <v>46122.65644733796</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.489798298615</v>
+        <v>46122.65646496528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4152,13 +4152,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.47320453703</v>
+        <v>46073.639871203704</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.5370488426</v>
+        <v>46122.703715509255</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.537065462966</v>
+        <v>46122.70373212963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4217,11 +4217,11 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.473204803246</v>
+        <v>46073.6398714699</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46195.7464409838</v>
+        <v>46195.913107650464</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4264,13 +4264,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.473205092596</v>
+        <v>46073.63987175926</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.327605011575</v>
+        <v>46128.49427167824</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.32761921296</v>
+        <v>46128.49428587963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4329,13 +4329,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.473205381946</v>
+        <v>46073.63987204861</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.71442625</v>
+        <v>46191.881092916665</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.50980561343</v>
+        <v>46194.67647228009</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4394,13 +4394,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4732056713</v>
+        <v>46073.63987233797</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.746432569445</v>
+        <v>46195.91309923611</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.74643462963</v>
+        <v>46195.9131012963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4457,11 +4457,11 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.473205937495</v>
+        <v>46073.639872604166</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46193.39767265046</v>
+        <v>46193.564339317134</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4504,13 +4504,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.47320619213</v>
+        <v>46073.639872858796</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.39765265046</v>
+        <v>46193.56431931713</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.50987547454</v>
+        <v>46194.6765421412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4569,13 +4569,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48240732639</v>
+        <v>46128.64907399306</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.482422650464</v>
+        <v>46128.64908931713</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4632,13 +4632,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.473202939815</v>
+        <v>46073.639869606486</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.39766754629</v>
+        <v>46193.56433421296</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.50992596065</v>
+        <v>46194.676592627315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4697,13 +4697,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.47320324074</v>
+        <v>46073.639869907405</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.490245243054</v>
+        <v>46122.656911909726</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.49026456018</v>
+        <v>46122.656931226855</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4760,11 +4760,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.47320353009</v>
+        <v>46073.639870196756</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46197.2522158912</v>
+        <v>46197.418882557875</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4807,13 +4807,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.447371064816</v>
+        <v>46193.61403773148</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.74644228009</v>
+        <v>46195.913108946756</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4872,13 +4872,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.47320417824</v>
+        <v>46073.63987084491</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.44741258102</v>
+        <v>46193.61407924768</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.44741420139</v>
+        <v>46193.61408086805</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4935,13 +4935,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.44742328704</v>
+        <v>46193.6140899537</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.447429479165</v>
+        <v>46193.61409614583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5000,13 +5000,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4732047338</v>
+        <v>46073.63987140046</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.44743372685</v>
+        <v>46193.61410039352</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.44743560185</v>
+        <v>46193.61410226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5065,13 +5065,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.47320501157</v>
+        <v>46073.63987167824</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.401569016205</v>
+        <v>46195.56823568287</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.401571168986</v>
+        <v>46195.56823783564</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5128,13 +5128,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.473205277776</v>
+        <v>46073.63987194444</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.25220809028</v>
+        <v>46197.41887475694</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.25221045139</v>
+        <v>46197.418877118056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5191,11 +5191,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.473202106485</v>
+        <v>46073.63986877315</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.54139027778</v>
+        <v>46197.708056944444</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5238,11 +5238,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46197.55406243056</v>
+        <v>46197.72072909722</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5299,13 +5299,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.473202905094</v>
+        <v>46073.63986957176</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.531424479166</v>
+        <v>46197.69809114584</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.53142733796</v>
+        <v>46197.698094004634</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5362,13 +5362,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.47320325232</v>
+        <v>46073.63986991898</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.54138311342</v>
+        <v>46197.70804978009</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.54138488426</v>
+        <v>46197.70805155093</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5425,11 +5425,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.473203587964</v>
+        <v>46073.63987025463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.54138938658</v>
+        <v>46197.70805605324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5486,11 +5486,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.47320392361</v>
+        <v>46073.63987059028</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.47486043982</v>
+        <v>46083.641527106476</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>
@@ -5533,11 +5533,11 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.47320424768</v>
+        <v>46073.639870914354</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.679287465275</v>
+        <v>46090.845954131946</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5596,11 +5596,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.47320460648</v>
+        <v>46073.639871273146</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.61326695602</v>
+        <v>46107.77993362269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5659,11 +5659,11 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.51352017361</v>
+        <v>46090.680186840276</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.52080292824</v>
+        <v>46090.68746959491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5706,11 +5706,11 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.51365603009</v>
+        <v>46090.68032269676</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.679375949076</v>
+        <v>46090.84604261574</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5769,11 +5769,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.51372481481</v>
+        <v>46090.68039148148</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.67937304398</v>
+        <v>46090.84603971065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -3975,9 +3975,11 @@
       <c r="B45" s="8">
         <v>46090.67984755787</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46198.56751383102</v>
+      </c>
       <c r="D45" s="8">
-        <v>46195.56824368055</v>
+        <v>46198.567517812495</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -5134,7 +5136,7 @@
         <v>46197.41887475694</v>
       </c>
       <c r="D64" s="5">
-        <v>46197.418877118056</v>
+        <v>46198.567522557874</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -4221,9 +4221,11 @@
       <c r="B49" s="8">
         <v>46073.6398714699</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46204.762843495366</v>
+      </c>
       <c r="D49" s="8">
-        <v>46195.913107650464</v>
+        <v>46204.7628446875</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4461,9 +4463,11 @@
       <c r="B53" s="8">
         <v>46073.639872604166</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46204.76285167824</v>
+      </c>
       <c r="D53" s="8">
-        <v>46193.564339317134</v>
+        <v>46204.76285297454</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4764,9 +4768,11 @@
       <c r="B58" s="5">
         <v>46073.639870196756</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46204.762805509265</v>
+      </c>
       <c r="D58" s="5">
-        <v>46197.418882557875</v>
+        <v>46204.762806909726</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -5197,7 +5203,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.708056944444</v>
+        <v>46204.76253861111</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5242,9 +5248,11 @@
       <c r="B66" s="5">
         <v>46073.63986921296</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46204.76252967592</v>
+      </c>
       <c r="D66" s="5">
-        <v>46197.72072909722</v>
+        <v>46204.76253261574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5307,7 +5315,7 @@
         <v>46197.69809114584</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.698094004634</v>
+        <v>46204.76253736111</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1444,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.63986869213</v>
+        <v>46073.47320202546</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.717724710645</v>
+        <v>46092.55105804398</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.839536643514</v>
+        <v>46134.67286997685</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1493,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.63986902778</v>
+        <v>46073.473202361114</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.717694618055</v>
+        <v>46092.551027951384</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.877865057875</v>
+        <v>46133.711198391204</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1558,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.63986934027</v>
+        <v>46073.47320267362</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.717695127314</v>
+        <v>46092.55102846065</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.71772585648</v>
+        <v>46092.55105918982</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1623,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.63986962963</v>
+        <v>46073.47320296297</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.717695555555</v>
+        <v>46092.55102888889</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.71772572916</v>
+        <v>46092.551059062505</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1688,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.639869942126</v>
+        <v>46073.47320327546</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.717695960644</v>
+        <v>46092.55102929398</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.78363827546</v>
+        <v>46100.6169716088</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1753,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.63987023148</v>
+        <v>46073.47320356482</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.71769665509</v>
+        <v>46092.551029988426</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.71772622685</v>
+        <v>46092.55105956018</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1818,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.639870520834</v>
+        <v>46073.47320385417</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.64914818287</v>
+        <v>46128.4824815162</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.649159872686</v>
+        <v>46128.482493206015</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1871,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.63987082176</v>
+        <v>46073.47320415509</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.61935167824</v>
+        <v>46099.45268501157</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.619374120375</v>
+        <v>46099.4527074537</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1936,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.63987108796</v>
+        <v>46073.4732044213</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.64913424768</v>
+        <v>46128.48246758102</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.64915</v>
+        <v>46128.48248333333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2001,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.63987138889</v>
+        <v>46073.47320472222</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.779946180555</v>
+        <v>46107.613279513884</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.8394806713</v>
+        <v>46134.67281400463</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2050,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.63986841435</v>
+        <v>46073.473201747685</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.55055525463</v>
+        <v>46097.38388858797</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.550571608794</v>
+        <v>46097.38390494213</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2115,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.63986943287</v>
+        <v>46073.4732027662</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.77985594908</v>
+        <v>46107.613189282405</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.77987517361</v>
+        <v>46107.61320850694</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2180,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.63987</v>
+        <v>46073.473203333335</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.550767719906</v>
+        <v>46097.38410105324</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.5507822338</v>
+        <v>46097.384115567125</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2245,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.6398705787</v>
+        <v>46073.473203912035</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.77992613426</v>
+        <v>46107.61325946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.77994740741</v>
+        <v>46107.61328074074</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2310,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.63987087963</v>
+        <v>46073.47320421296</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.780059386576</v>
+        <v>46107.61339271991</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.780072222224</v>
+        <v>46107.61340555556</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.63987116898</v>
+        <v>46073.47320450231</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.78000262732</v>
+        <v>46107.61333596065</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.780019328704</v>
+        <v>46107.61335266204</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2428,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.63987179398</v>
+        <v>46073.47320512732</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.550614884254</v>
+        <v>46097.3839482176</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.55063</v>
+        <v>46097.383963333334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2493,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.63987206019</v>
+        <v>46073.473205393515</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.619815949074</v>
+        <v>46099.4531492824</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.61983109954</v>
+        <v>46099.45316443287</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2558,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.63987269676</v>
+        <v>46073.47320603009</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.780038854165</v>
+        <v>46107.6133721875</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.83677627315</v>
+        <v>46134.67010960648</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2623,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.639868287035</v>
+        <v>46073.47320162037</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55083957176</v>
+        <v>46097.38417290509</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.64059725695</v>
+        <v>46197.47393059028</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.63986866898</v>
+        <v>46073.473202002315</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.60291127315</v>
+        <v>46112.43624460648</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.83959192129</v>
+        <v>46134.67292525463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2737,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.63986895833</v>
+        <v>46073.473202291665</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.78015736111</v>
+        <v>46107.61349069445</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.780284016204</v>
+        <v>46107.61361734953</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2802,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.78008822916</v>
+        <v>46107.6134215625</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.78008986111</v>
+        <v>46107.613423194445</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2863,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.63986952546</v>
+        <v>46073.4732028588</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.78014291667</v>
+        <v>46107.61347625</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.78014446759</v>
+        <v>46107.61347780093</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2924,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.639869861116</v>
+        <v>46073.473203194444</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.64901734954</v>
+        <v>46128.48235068287</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.64903339121</v>
+        <v>46128.48236672454</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2989,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.63987017361</v>
+        <v>46073.47320350695</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.61991980324</v>
+        <v>46099.45325313657</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.61992293982</v>
+        <v>46099.45325627315</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3050,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.649000590274</v>
+        <v>46128.48233392361</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.6490021412</v>
+        <v>46128.48233547454</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3111,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.639870810184</v>
+        <v>46073.47320414352</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.84297413194</v>
+        <v>46125.67630746528</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.84297541667</v>
+        <v>46125.67630875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3176,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.78179094907</v>
+        <v>46107.61512428241</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.781792395836</v>
+        <v>46107.615125729164</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3237,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.639868321756</v>
+        <v>46073.47320165509</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.78183342592</v>
+        <v>46107.615166759264</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.781834988426</v>
+        <v>46107.61516832176</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3298,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.63986865741</v>
+        <v>46073.47320199074</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.78100310185</v>
+        <v>46107.61433643519</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.781017974536</v>
+        <v>46107.61435130787</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3363,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.639868935184</v>
+        <v>46073.47320226852</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.55069820602</v>
+        <v>46097.38403153935</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.550699872685</v>
+        <v>46097.38403320602</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3424,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.78094795139</v>
+        <v>46107.614281284725</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.7809494213</v>
+        <v>46107.61428275463</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3485,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.63986949074</v>
+        <v>46073.47320282407</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.780985590274</v>
+        <v>46107.61431892361</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.780987465274</v>
+        <v>46107.61432079861</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3546,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.63986978009</v>
+        <v>46073.473203113426</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.550948819444</v>
+        <v>46097.38428215278</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.550965891205</v>
+        <v>46097.38429922453</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3611,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.63987009259</v>
+        <v>46073.47320342592</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.550895844906</v>
+        <v>46097.38422917824</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.550897141205</v>
+        <v>46097.384230474534</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3672,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.63987039352</v>
+        <v>46073.473203726855</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.550933923616</v>
+        <v>46097.384267256944</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.55093533565</v>
+        <v>46097.38426866898</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3733,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.63987067129</v>
+        <v>46073.47320400463</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.839630381946</v>
+        <v>46134.672963715275</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3780,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.639870983796</v>
+        <v>46073.473204317124</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.51873575231</v>
+        <v>46114.35206908565</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51875664352</v>
+        <v>46114.35208997685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3845,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.6398703125</v>
+        <v>46073.47320364583</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.79026576389</v>
+        <v>46114.62359909722</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.79028366898</v>
+        <v>46114.62361700232</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3910,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.679795104166</v>
+        <v>46090.513128437495</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.79031591435</v>
+        <v>46114.62364924769</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.79033271991</v>
+        <v>46114.623666053245</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3973,13 +3973,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.67984755787</v>
+        <v>46090.513180891205</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.56751383102</v>
+        <v>46198.40084716435</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.567517812495</v>
+        <v>46198.40085114584</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4036,13 +4036,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.639870659725</v>
+        <v>46073.47320399305</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.70373234954</v>
+        <v>46122.537065682875</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.70375010416</v>
+        <v>46122.5370834375</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4089,13 +4089,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.6398709375</v>
+        <v>46073.473204270835</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.65644733796</v>
+        <v>46122.4897806713</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.65646496528</v>
+        <v>46122.489798298615</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4154,13 +4154,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.639871203704</v>
+        <v>46073.47320453703</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.703715509255</v>
+        <v>46122.5370488426</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.70373212963</v>
+        <v>46122.537065462966</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4219,13 +4219,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.6398714699</v>
+        <v>46073.473204803246</v>
       </c>
       <c r="C49" s="8">
-        <v>46204.762843495366</v>
+        <v>46204.59617682871</v>
       </c>
       <c r="D49" s="8">
-        <v>46204.7628446875</v>
+        <v>46204.59617802083</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4268,13 +4268,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.63987175926</v>
+        <v>46073.473205092596</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.49427167824</v>
+        <v>46128.327605011575</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.49428587963</v>
+        <v>46128.32761921296</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4333,13 +4333,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.63987204861</v>
+        <v>46073.473205381946</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.881092916665</v>
+        <v>46191.71442625</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.67647228009</v>
+        <v>46194.50980561343</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4398,13 +4398,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.63987233797</v>
+        <v>46073.4732056713</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.91309923611</v>
+        <v>46195.746432569445</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.9131012963</v>
+        <v>46195.74643462963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4461,13 +4461,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.639872604166</v>
+        <v>46073.473205937495</v>
       </c>
       <c r="C53" s="8">
-        <v>46204.76285167824</v>
+        <v>46204.59618501157</v>
       </c>
       <c r="D53" s="8">
-        <v>46204.76285297454</v>
+        <v>46204.59618630787</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4510,13 +4510,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.639872858796</v>
+        <v>46073.47320619213</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.56431931713</v>
+        <v>46193.39765265046</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.6765421412</v>
+        <v>46194.50987547454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4575,13 +4575,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.63986924769</v>
+        <v>46073.47320258102</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.64907399306</v>
+        <v>46128.48240732639</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.64908931713</v>
+        <v>46128.482422650464</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4638,13 +4638,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.639869606486</v>
+        <v>46073.473202939815</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.56433421296</v>
+        <v>46193.39766754629</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.676592627315</v>
+        <v>46194.50992596065</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4703,13 +4703,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.639869907405</v>
+        <v>46073.47320324074</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.656911909726</v>
+        <v>46122.490245243054</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.656931226855</v>
+        <v>46122.49026456018</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4766,13 +4766,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.639870196756</v>
+        <v>46073.47320353009</v>
       </c>
       <c r="C58" s="5">
-        <v>46204.762805509265</v>
+        <v>46204.59613884259</v>
       </c>
       <c r="D58" s="5">
-        <v>46204.762806909726</v>
+        <v>46204.596140243055</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4815,13 +4815,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.639870486106</v>
+        <v>46073.47320381945</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.61403773148</v>
+        <v>46193.447371064816</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.913108946756</v>
+        <v>46195.74644228009</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4880,13 +4880,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.63987084491</v>
+        <v>46073.47320417824</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.61407924768</v>
+        <v>46193.44741258102</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.61408086805</v>
+        <v>46193.44741420139</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4943,13 +4943,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.63987109954</v>
+        <v>46073.47320443287</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.6140899537</v>
+        <v>46193.44742328704</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.61409614583</v>
+        <v>46193.447429479165</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5008,13 +5008,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.63987140046</v>
+        <v>46073.4732047338</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.61410039352</v>
+        <v>46193.44743372685</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.61410226852</v>
+        <v>46193.44743560185</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5073,13 +5073,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.63987167824</v>
+        <v>46073.47320501157</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.56823568287</v>
+        <v>46195.401569016205</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.56823783564</v>
+        <v>46195.401571168986</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5136,13 +5136,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.63987194444</v>
+        <v>46073.473205277776</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.41887475694</v>
+        <v>46197.25220809028</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.567522557874</v>
+        <v>46198.4008558912</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5199,11 +5199,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.63986877315</v>
+        <v>46073.473202106485</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46204.76253861111</v>
+        <v>46204.595871944446</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5246,13 +5246,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.63986921296</v>
+        <v>46073.473202546294</v>
       </c>
       <c r="C66" s="5">
-        <v>46204.76252967592</v>
+        <v>46204.595863009265</v>
       </c>
       <c r="D66" s="5">
-        <v>46204.76253261574</v>
+        <v>46204.59586594907</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5309,13 +5309,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.63986957176</v>
+        <v>46073.473202905094</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.69809114584</v>
+        <v>46197.531424479166</v>
       </c>
       <c r="D67" s="8">
-        <v>46204.76253736111</v>
+        <v>46204.595870694444</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5372,13 +5372,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.63986991898</v>
+        <v>46073.47320325232</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.70804978009</v>
+        <v>46197.54138311342</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.70805155093</v>
+        <v>46197.54138488426</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5435,11 +5435,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.63987025463</v>
+        <v>46073.473203587964</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.70805605324</v>
+        <v>46197.54138938658</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5496,11 +5496,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.63987059028</v>
+        <v>46073.47320392361</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.641527106476</v>
+        <v>46083.47486043982</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>
@@ -5543,11 +5543,11 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.639870914354</v>
+        <v>46073.47320424768</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.845954131946</v>
+        <v>46090.679287465275</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5606,11 +5606,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.639871273146</v>
+        <v>46073.47320460648</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.77993362269</v>
+        <v>46107.61326695602</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5669,11 +5669,11 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.680186840276</v>
+        <v>46090.51352017361</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.68746959491</v>
+        <v>46090.52080292824</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5716,11 +5716,11 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.68032269676</v>
+        <v>46090.51365603009</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.84604261574</v>
+        <v>46090.679375949076</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5779,11 +5779,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.68039148148</v>
+        <v>46090.51372481481</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.84603971065</v>
+        <v>46090.67937304398</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -1444,13 +1444,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46073.47320202546</v>
+        <v>46073.63986869213</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55105804398</v>
+        <v>46092.717724710645</v>
       </c>
       <c r="D4" s="5">
-        <v>46134.67286997685</v>
+        <v>46134.839536643514</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1493,13 +1493,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46073.473202361114</v>
+        <v>46073.63986902778</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.551027951384</v>
+        <v>46092.717694618055</v>
       </c>
       <c r="D5" s="8">
-        <v>46133.711198391204</v>
+        <v>46133.877865057875</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1558,13 +1558,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46073.47320267362</v>
+        <v>46073.63986934027</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55102846065</v>
+        <v>46092.717695127314</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.55105918982</v>
+        <v>46092.71772585648</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1623,13 +1623,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46073.47320296297</v>
+        <v>46073.63986962963</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.55102888889</v>
+        <v>46092.717695555555</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.551059062505</v>
+        <v>46092.71772572916</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -1688,13 +1688,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46073.47320327546</v>
+        <v>46073.639869942126</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55102929398</v>
+        <v>46092.717695960644</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.6169716088</v>
+        <v>46100.78363827546</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -1753,13 +1753,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46073.47320356482</v>
+        <v>46073.63987023148</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.551029988426</v>
+        <v>46092.71769665509</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.55105956018</v>
+        <v>46092.71772622685</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -1818,13 +1818,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46073.47320385417</v>
+        <v>46073.639870520834</v>
       </c>
       <c r="C10" s="5">
-        <v>46128.4824815162</v>
+        <v>46128.64914818287</v>
       </c>
       <c r="D10" s="5">
-        <v>46128.482493206015</v>
+        <v>46128.649159872686</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1871,13 +1871,13 @@
         <v>48</v>
       </c>
       <c r="B11" s="8">
-        <v>46073.47320415509</v>
+        <v>46073.63987082176</v>
       </c>
       <c r="C11" s="8">
-        <v>46099.45268501157</v>
+        <v>46099.61935167824</v>
       </c>
       <c r="D11" s="8">
-        <v>46099.4527074537</v>
+        <v>46099.619374120375</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
@@ -1936,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46073.4732044213</v>
+        <v>46073.63987108796</v>
       </c>
       <c r="C12" s="5">
-        <v>46128.48246758102</v>
+        <v>46128.64913424768</v>
       </c>
       <c r="D12" s="5">
-        <v>46128.48248333333</v>
+        <v>46128.64915</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2001,13 +2001,13 @@
         <v>57</v>
       </c>
       <c r="B13" s="8">
-        <v>46073.47320472222</v>
+        <v>46073.63987138889</v>
       </c>
       <c r="C13" s="8">
-        <v>46107.613279513884</v>
+        <v>46107.779946180555</v>
       </c>
       <c r="D13" s="8">
-        <v>46134.67281400463</v>
+        <v>46134.8394806713</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>58</v>
@@ -2050,13 +2050,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46073.473201747685</v>
+        <v>46073.63986841435</v>
       </c>
       <c r="C14" s="5">
-        <v>46097.38388858797</v>
+        <v>46097.55055525463</v>
       </c>
       <c r="D14" s="5">
-        <v>46097.38390494213</v>
+        <v>46097.550571608794</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2115,13 +2115,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46073.4732027662</v>
+        <v>46073.63986943287</v>
       </c>
       <c r="C15" s="8">
-        <v>46107.613189282405</v>
+        <v>46107.77985594908</v>
       </c>
       <c r="D15" s="8">
-        <v>46107.61320850694</v>
+        <v>46107.77987517361</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2180,13 +2180,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46073.473203333335</v>
+        <v>46073.63987</v>
       </c>
       <c r="C16" s="5">
-        <v>46097.38410105324</v>
+        <v>46097.550767719906</v>
       </c>
       <c r="D16" s="5">
-        <v>46097.384115567125</v>
+        <v>46097.5507822338</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2245,13 +2245,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46073.473203912035</v>
+        <v>46073.6398705787</v>
       </c>
       <c r="C17" s="8">
-        <v>46107.61325946759</v>
+        <v>46107.77992613426</v>
       </c>
       <c r="D17" s="8">
-        <v>46107.61328074074</v>
+        <v>46107.77994740741</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2310,13 +2310,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46073.47320421296</v>
+        <v>46073.63987087963</v>
       </c>
       <c r="C18" s="5">
-        <v>46107.61339271991</v>
+        <v>46107.780059386576</v>
       </c>
       <c r="D18" s="5">
-        <v>46107.61340555556</v>
+        <v>46107.780072222224</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2363,13 +2363,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46073.47320450231</v>
+        <v>46073.63987116898</v>
       </c>
       <c r="C19" s="8">
-        <v>46107.61333596065</v>
+        <v>46107.78000262732</v>
       </c>
       <c r="D19" s="8">
-        <v>46107.61335266204</v>
+        <v>46107.780019328704</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2428,13 +2428,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46073.47320512732</v>
+        <v>46073.63987179398</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.3839482176</v>
+        <v>46097.550614884254</v>
       </c>
       <c r="D20" s="5">
-        <v>46097.383963333334</v>
+        <v>46097.55063</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -2493,13 +2493,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46073.473205393515</v>
+        <v>46073.63987206019</v>
       </c>
       <c r="C21" s="8">
-        <v>46099.4531492824</v>
+        <v>46099.619815949074</v>
       </c>
       <c r="D21" s="8">
-        <v>46099.45316443287</v>
+        <v>46099.61983109954</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -2558,13 +2558,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46073.47320603009</v>
+        <v>46073.63987269676</v>
       </c>
       <c r="C22" s="5">
-        <v>46107.6133721875</v>
+        <v>46107.780038854165</v>
       </c>
       <c r="D22" s="5">
-        <v>46134.67010960648</v>
+        <v>46134.83677627315</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -2623,13 +2623,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46073.47320162037</v>
+        <v>46073.639868287035</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38417290509</v>
+        <v>46097.55083957176</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.47393059028</v>
+        <v>46197.64059725695</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -2688,13 +2688,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46073.473202002315</v>
+        <v>46073.63986866898</v>
       </c>
       <c r="C24" s="5">
-        <v>46112.43624460648</v>
+        <v>46112.60291127315</v>
       </c>
       <c r="D24" s="5">
-        <v>46134.67292525463</v>
+        <v>46134.83959192129</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -2737,13 +2737,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46073.473202291665</v>
+        <v>46073.63986895833</v>
       </c>
       <c r="C25" s="8">
-        <v>46107.61349069445</v>
+        <v>46107.78015736111</v>
       </c>
       <c r="D25" s="8">
-        <v>46107.61361734953</v>
+        <v>46107.780284016204</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -2802,13 +2802,13 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C26" s="5">
-        <v>46107.6134215625</v>
+        <v>46107.78008822916</v>
       </c>
       <c r="D26" s="5">
-        <v>46107.613423194445</v>
+        <v>46107.78008986111</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>102</v>
@@ -2863,13 +2863,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46073.4732028588</v>
+        <v>46073.63986952546</v>
       </c>
       <c r="C27" s="8">
-        <v>46107.61347625</v>
+        <v>46107.78014291667</v>
       </c>
       <c r="D27" s="8">
-        <v>46107.61347780093</v>
+        <v>46107.78014446759</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2924,13 +2924,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46073.473203194444</v>
+        <v>46073.639869861116</v>
       </c>
       <c r="C28" s="5">
-        <v>46128.48235068287</v>
+        <v>46128.64901734954</v>
       </c>
       <c r="D28" s="5">
-        <v>46128.48236672454</v>
+        <v>46128.64903339121</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2989,13 +2989,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46073.47320350695</v>
+        <v>46073.63987017361</v>
       </c>
       <c r="C29" s="8">
-        <v>46099.45325313657</v>
+        <v>46099.61991980324</v>
       </c>
       <c r="D29" s="8">
-        <v>46099.45325627315</v>
+        <v>46099.61992293982</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3050,13 +3050,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C30" s="5">
-        <v>46128.48233392361</v>
+        <v>46128.649000590274</v>
       </c>
       <c r="D30" s="5">
-        <v>46128.48233547454</v>
+        <v>46128.6490021412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3111,13 +3111,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46073.47320414352</v>
+        <v>46073.639870810184</v>
       </c>
       <c r="C31" s="8">
-        <v>46125.67630746528</v>
+        <v>46125.84297413194</v>
       </c>
       <c r="D31" s="8">
-        <v>46125.67630875</v>
+        <v>46125.84297541667</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3176,13 +3176,13 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C32" s="5">
-        <v>46107.61512428241</v>
+        <v>46107.78179094907</v>
       </c>
       <c r="D32" s="5">
-        <v>46107.615125729164</v>
+        <v>46107.781792395836</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3237,13 +3237,13 @@
         <v>124</v>
       </c>
       <c r="B33" s="8">
-        <v>46073.47320165509</v>
+        <v>46073.639868321756</v>
       </c>
       <c r="C33" s="8">
-        <v>46107.615166759264</v>
+        <v>46107.78183342592</v>
       </c>
       <c r="D33" s="8">
-        <v>46107.61516832176</v>
+        <v>46107.781834988426</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>125</v>
@@ -3298,13 +3298,13 @@
         <v>127</v>
       </c>
       <c r="B34" s="5">
-        <v>46073.47320199074</v>
+        <v>46073.63986865741</v>
       </c>
       <c r="C34" s="5">
-        <v>46107.61433643519</v>
+        <v>46107.78100310185</v>
       </c>
       <c r="D34" s="5">
-        <v>46107.61435130787</v>
+        <v>46107.781017974536</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>128</v>
@@ -3363,13 +3363,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46073.47320226852</v>
+        <v>46073.639868935184</v>
       </c>
       <c r="C35" s="8">
-        <v>46097.38403153935</v>
+        <v>46097.55069820602</v>
       </c>
       <c r="D35" s="8">
-        <v>46097.38403320602</v>
+        <v>46097.550699872685</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -3424,13 +3424,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C36" s="5">
-        <v>46107.614281284725</v>
+        <v>46107.78094795139</v>
       </c>
       <c r="D36" s="5">
-        <v>46107.61428275463</v>
+        <v>46107.7809494213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -3485,13 +3485,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46073.47320282407</v>
+        <v>46073.63986949074</v>
       </c>
       <c r="C37" s="8">
-        <v>46107.61431892361</v>
+        <v>46107.780985590274</v>
       </c>
       <c r="D37" s="8">
-        <v>46107.61432079861</v>
+        <v>46107.780987465274</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -3546,13 +3546,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46073.473203113426</v>
+        <v>46073.63986978009</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.38428215278</v>
+        <v>46097.550948819444</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38429922453</v>
+        <v>46097.550965891205</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -3611,13 +3611,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46073.47320342592</v>
+        <v>46073.63987009259</v>
       </c>
       <c r="C39" s="8">
-        <v>46097.38422917824</v>
+        <v>46097.550895844906</v>
       </c>
       <c r="D39" s="8">
-        <v>46097.384230474534</v>
+        <v>46097.550897141205</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -3672,13 +3672,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46073.473203726855</v>
+        <v>46073.63987039352</v>
       </c>
       <c r="C40" s="5">
-        <v>46097.384267256944</v>
+        <v>46097.550933923616</v>
       </c>
       <c r="D40" s="5">
-        <v>46097.38426866898</v>
+        <v>46097.55093533565</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -3733,11 +3733,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46073.47320400463</v>
+        <v>46073.63987067129</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46134.672963715275</v>
+        <v>46134.839630381946</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3780,13 +3780,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46073.473204317124</v>
+        <v>46073.639870983796</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.35206908565</v>
+        <v>46114.51873575231</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.35208997685</v>
+        <v>46114.51875664352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3845,13 +3845,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46073.47320364583</v>
+        <v>46073.6398703125</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.62359909722</v>
+        <v>46114.79026576389</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.62361700232</v>
+        <v>46114.79028366898</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3910,13 +3910,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46090.513128437495</v>
+        <v>46090.679795104166</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.62364924769</v>
+        <v>46114.79031591435</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.623666053245</v>
+        <v>46114.79033271991</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3973,13 +3973,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46090.513180891205</v>
+        <v>46090.67984755787</v>
       </c>
       <c r="C45" s="8">
-        <v>46198.40084716435</v>
+        <v>46198.56751383102</v>
       </c>
       <c r="D45" s="8">
-        <v>46198.40085114584</v>
+        <v>46198.567517812495</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4036,13 +4036,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46073.47320399305</v>
+        <v>46073.639870659725</v>
       </c>
       <c r="C46" s="5">
-        <v>46122.537065682875</v>
+        <v>46122.70373234954</v>
       </c>
       <c r="D46" s="5">
-        <v>46122.5370834375</v>
+        <v>46122.70375010416</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4089,13 +4089,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46073.473204270835</v>
+        <v>46073.6398709375</v>
       </c>
       <c r="C47" s="8">
-        <v>46122.4897806713</v>
+        <v>46122.65644733796</v>
       </c>
       <c r="D47" s="8">
-        <v>46122.489798298615</v>
+        <v>46122.65646496528</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4154,13 +4154,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46073.47320453703</v>
+        <v>46073.639871203704</v>
       </c>
       <c r="C48" s="5">
-        <v>46122.5370488426</v>
+        <v>46122.703715509255</v>
       </c>
       <c r="D48" s="5">
-        <v>46122.537065462966</v>
+        <v>46122.70373212963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4219,13 +4219,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46073.473204803246</v>
+        <v>46073.6398714699</v>
       </c>
       <c r="C49" s="8">
-        <v>46204.59617682871</v>
+        <v>46204.762843495366</v>
       </c>
       <c r="D49" s="8">
-        <v>46204.59617802083</v>
+        <v>46204.7628446875</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4268,13 +4268,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46073.473205092596</v>
+        <v>46073.63987175926</v>
       </c>
       <c r="C50" s="5">
-        <v>46128.327605011575</v>
+        <v>46128.49427167824</v>
       </c>
       <c r="D50" s="5">
-        <v>46128.32761921296</v>
+        <v>46128.49428587963</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4333,13 +4333,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46073.473205381946</v>
+        <v>46073.63987204861</v>
       </c>
       <c r="C51" s="8">
-        <v>46191.71442625</v>
+        <v>46191.881092916665</v>
       </c>
       <c r="D51" s="8">
-        <v>46194.50980561343</v>
+        <v>46194.67647228009</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4398,13 +4398,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46073.4732056713</v>
+        <v>46073.63987233797</v>
       </c>
       <c r="C52" s="5">
-        <v>46195.746432569445</v>
+        <v>46195.91309923611</v>
       </c>
       <c r="D52" s="5">
-        <v>46195.74643462963</v>
+        <v>46195.9131012963</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4461,13 +4461,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46073.473205937495</v>
+        <v>46073.639872604166</v>
       </c>
       <c r="C53" s="8">
-        <v>46204.59618501157</v>
+        <v>46204.76285167824</v>
       </c>
       <c r="D53" s="8">
-        <v>46204.59618630787</v>
+        <v>46204.76285297454</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4510,13 +4510,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46073.47320619213</v>
+        <v>46073.639872858796</v>
       </c>
       <c r="C54" s="5">
-        <v>46193.39765265046</v>
+        <v>46193.56431931713</v>
       </c>
       <c r="D54" s="5">
-        <v>46194.50987547454</v>
+        <v>46194.6765421412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4575,13 +4575,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46073.47320258102</v>
+        <v>46073.63986924769</v>
       </c>
       <c r="C55" s="8">
-        <v>46128.48240732639</v>
+        <v>46128.64907399306</v>
       </c>
       <c r="D55" s="8">
-        <v>46128.482422650464</v>
+        <v>46128.64908931713</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>55</v>
@@ -4638,13 +4638,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46073.473202939815</v>
+        <v>46073.639869606486</v>
       </c>
       <c r="C56" s="5">
-        <v>46193.39766754629</v>
+        <v>46193.56433421296</v>
       </c>
       <c r="D56" s="5">
-        <v>46194.50992596065</v>
+        <v>46194.676592627315</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4703,13 +4703,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46073.47320324074</v>
+        <v>46073.639869907405</v>
       </c>
       <c r="C57" s="8">
-        <v>46122.490245243054</v>
+        <v>46122.656911909726</v>
       </c>
       <c r="D57" s="8">
-        <v>46122.49026456018</v>
+        <v>46122.656931226855</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4766,13 +4766,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46073.47320353009</v>
+        <v>46073.639870196756</v>
       </c>
       <c r="C58" s="5">
-        <v>46204.59613884259</v>
+        <v>46204.762805509265</v>
       </c>
       <c r="D58" s="5">
-        <v>46204.596140243055</v>
+        <v>46204.762806909726</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4815,13 +4815,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46073.47320381945</v>
+        <v>46073.639870486106</v>
       </c>
       <c r="C59" s="8">
-        <v>46193.447371064816</v>
+        <v>46193.61403773148</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.74644228009</v>
+        <v>46195.913108946756</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4880,13 +4880,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46073.47320417824</v>
+        <v>46073.63987084491</v>
       </c>
       <c r="C60" s="5">
-        <v>46193.44741258102</v>
+        <v>46193.61407924768</v>
       </c>
       <c r="D60" s="5">
-        <v>46193.44741420139</v>
+        <v>46193.61408086805</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -4943,13 +4943,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46073.47320443287</v>
+        <v>46073.63987109954</v>
       </c>
       <c r="C61" s="8">
-        <v>46193.44742328704</v>
+        <v>46193.6140899537</v>
       </c>
       <c r="D61" s="8">
-        <v>46193.447429479165</v>
+        <v>46193.61409614583</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5008,13 +5008,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46073.4732047338</v>
+        <v>46073.63987140046</v>
       </c>
       <c r="C62" s="5">
-        <v>46193.44743372685</v>
+        <v>46193.61410039352</v>
       </c>
       <c r="D62" s="5">
-        <v>46193.44743560185</v>
+        <v>46193.61410226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5073,13 +5073,13 @@
         <v>228</v>
       </c>
       <c r="B63" s="8">
-        <v>46073.47320501157</v>
+        <v>46073.63987167824</v>
       </c>
       <c r="C63" s="8">
-        <v>46195.401569016205</v>
+        <v>46195.56823568287</v>
       </c>
       <c r="D63" s="8">
-        <v>46195.401571168986</v>
+        <v>46195.56823783564</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5136,13 +5136,13 @@
         <v>231</v>
       </c>
       <c r="B64" s="5">
-        <v>46073.473205277776</v>
+        <v>46073.63987194444</v>
       </c>
       <c r="C64" s="5">
-        <v>46197.25220809028</v>
+        <v>46197.41887475694</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.4008558912</v>
+        <v>46198.567522557874</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>170</v>
@@ -5199,11 +5199,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46073.473202106485</v>
+        <v>46073.63986877315</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46204.595871944446</v>
+        <v>46204.76253861111</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5246,13 +5246,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46073.473202546294</v>
+        <v>46073.63986921296</v>
       </c>
       <c r="C66" s="5">
-        <v>46204.595863009265</v>
+        <v>46204.76252967592</v>
       </c>
       <c r="D66" s="5">
-        <v>46204.59586594907</v>
+        <v>46204.76253261574</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5309,13 +5309,13 @@
         <v>241</v>
       </c>
       <c r="B67" s="8">
-        <v>46073.473202905094</v>
+        <v>46073.63986957176</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.531424479166</v>
+        <v>46197.69809114584</v>
       </c>
       <c r="D67" s="8">
-        <v>46204.595870694444</v>
+        <v>46204.76253736111</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5372,13 +5372,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46073.47320325232</v>
+        <v>46073.63986991898</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.54138311342</v>
+        <v>46197.70804978009</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.54138488426</v>
+        <v>46197.70805155093</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5435,11 +5435,11 @@
         <v>248</v>
       </c>
       <c r="B69" s="8">
-        <v>46073.473203587964</v>
+        <v>46073.63987025463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.54138938658</v>
+        <v>46197.70805605324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>249</v>
@@ -5496,11 +5496,11 @@
         <v>251</v>
       </c>
       <c r="B70" s="5">
-        <v>46073.47320392361</v>
+        <v>46073.63987059028</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46083.47486043982</v>
+        <v>46083.641527106476</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>252</v>
@@ -5543,11 +5543,11 @@
         <v>254</v>
       </c>
       <c r="B71" s="8">
-        <v>46073.47320424768</v>
+        <v>46073.639870914354</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46090.679287465275</v>
+        <v>46090.845954131946</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>255</v>
@@ -5606,11 +5606,11 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46073.47320460648</v>
+        <v>46073.639871273146</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46107.61326695602</v>
+        <v>46107.77993362269</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5669,11 +5669,11 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.51352017361</v>
+        <v>46090.680186840276</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46090.52080292824</v>
+        <v>46090.68746959491</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>262</v>
@@ -5716,11 +5716,11 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.51365603009</v>
+        <v>46090.68032269676</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46090.679375949076</v>
+        <v>46090.84604261574</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>265</v>
@@ -5779,11 +5779,11 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.51372481481</v>
+        <v>46090.68039148148</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46090.67937304398</v>
+        <v>46090.84603971065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>

--- a/data/50001473 - MAPIMI.xlsx
+++ b/data/50001473 - MAPIMI.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="260">
   <si>
     <t>50001473 - MAPIMI</t>
   </si>
@@ -760,7 +760,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Gestion,Costo,Logistica:,Instalación componentes</t>
+    <t>Gestion,Costo,Logistica:</t>
   </si>
   <si>
     <t>1213378623901310</t>
@@ -791,30 +791,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213575386156318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en Marcha Servicios </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación componentes,Pruebas de instalación componentes </t>
-  </si>
-  <si>
-    <t>1213575386156320</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación componentes ,Puesta en Marcha Servicios </t>
-  </si>
-  <si>
-    <t>1213575386156322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación componentes </t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U75"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5436,7 +5412,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46197.70805605324</v>
+        <v>46240.72249984954</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5658,179 +5634,6 @@
         <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B73" s="8">
-        <v>46090.680186840276</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8">
-        <v>46090.68746959491</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q73" s="9"/>
-      <c r="R73" s="9"/>
-      <c r="S73" s="9"/>
-      <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B74" s="5">
-        <v>46090.68032269676</v>
-      </c>
-      <c r="C74" s="6"/>
-      <c r="D74" s="5">
-        <v>46090.84604261574</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I74" s="5">
-        <v>46024</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46034</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="P74" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46024</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46034</v>
-      </c>
-      <c r="S74" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B75" s="8">
-        <v>46090.68039148148</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="8">
-        <v>46090.84603971065</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I75" s="8">
-        <v>46035</v>
-      </c>
-      <c r="J75" s="8">
-        <v>46043</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q75" s="8">
-        <v>46035</v>
-      </c>
-      <c r="R75" s="8">
-        <v>46043</v>
-      </c>
-      <c r="S75" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="T75" s="9">
-        <v>0</v>
-      </c>
-      <c r="U75" s="10" t="s">
         <v>104</v>
       </c>
     </row>
